--- a/outputs/安排结果_第二轮.xlsx
+++ b/outputs/安排结果_第二轮.xlsx
@@ -468,19 +468,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F8, M3, M5, M7</t>
+          <t>F6, F7, M10, M8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F8(曹雅楠/原F9), M3(孙子涵), M5(周嘉铭), M7(郑明轩)</t>
+          <t>F6(You Lai), F7(April Cheng), M10(沈育嘉), M8(JIN XIE)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -492,22 +492,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F6, F9, M2, M9</t>
+          <t>F10, F8, M1, M4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F6(宋可欣), F9(彭思妍/原F10), M2(钱宇轩), M9(冯博文)</t>
+          <t>F10(胥夏), F8(Ellen Wan), M1(Chengzhi Peng), M4(刘泽翔)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F1, F2, M4, M6</t>
+          <t>F1, F2, M5, M9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F1(林雨桐), F2(何诗涵), M4(李俊熙), M6(吴泽宇)</t>
+          <t>F1(连璐), F2(ariel xiao), M5(Steven Lin), M9(Kevin Shen)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,22 +540,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F4, F5, F7, M8</t>
+          <t>F4, F9, M3, M7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F4(梁欣怡), F5(谢梦瑶), F7(唐婉清), M8(王景辰)</t>
+          <t>F4(wanlin zheng), F9(Ye Wang), M3(胡永昕), M7(张延)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -564,22 +564,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F3, M1, M10</t>
+          <t>F3, F5, M2, M6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>F3(高若曦), M1(赵浩然), M10(陈奕辰)</t>
+          <t>F3(蒲悠儿), F5(Yue Lin), M2(汪喆昊), M6(Yong Yang)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,22 +644,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M7(郑明轩)</t>
+          <t>M10(沈育嘉)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>F8(曹雅楠/原F9)</t>
+          <t>F7(April Cheng)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -668,7 +668,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -682,17 +682,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M5(周嘉铭)</t>
+          <t>M5(Steven Lin)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F8(曹雅楠/原F9)</t>
+          <t>F2(ariel xiao)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -701,7 +701,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -710,22 +710,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M3(孙子涵)</t>
+          <t>M9(Kevin Shen)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>F8(曹雅楠/原F9)</t>
+          <t>F2(ariel xiao)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -734,7 +734,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -743,22 +743,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F6(宋可欣)</t>
+          <t>M7(张延)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M9(冯博文)</t>
+          <t>F4(wanlin zheng)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -767,7 +767,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -776,22 +776,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F6(宋可欣)</t>
+          <t>F9(Ye Wang)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M2(钱宇轩)</t>
+          <t>M3(胡永昕)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -800,87 +800,87 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>互相喜欢</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>F4(wanlin zheng)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M3(胡永昕)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>互相喜欢</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>F9(彭思妍/原F10)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>M2(钱宇轩)</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>互相喜欢</t>
+          <t>单向喜欢</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F2(何诗涵)</t>
+          <t>M6(Yong Yang)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M4(李俊熙)</t>
+          <t>F3(蒲悠儿)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>互相喜欢</t>
+          <t>单向喜欢</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F1(林雨桐)</t>
+          <t>F5(Yue Lin)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -890,176 +890,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M6(吴泽宇)</t>
+          <t>M6(Yong Yang)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.666666666666667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>单向喜欢</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>F5(谢梦瑶)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>M8(王景辰)</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>互相喜欢</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>F4(梁欣怡)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>M8(王景辰)</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1.666666666666667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>互相喜欢</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>F7(唐婉清)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>M8(王景辰)</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1.666666666666667</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>单向喜欢</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>M10(陈奕辰)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>F3(高若曦)</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>互相喜欢</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>F3(高若曦)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>M1(赵浩然)</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1095,7 +930,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1105,7 +940,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
@@ -1125,7 +960,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1136,7 +971,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
